--- a/Assets/UnityExcelImporterX/Example/Excels/MsItems.xlsx
+++ b/Assets/UnityExcelImporterX/Example/Excels/MsItems.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <workbookPr filterPrivacy="1" codeName="ThisWorkbook" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
     <sheet name="item" sheetId="1" r:id="rId1"/>
@@ -20,11 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="102">
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -54,44 +50,386 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>name</t>
-  </si>
-  <si>
     <t>price</t>
   </si>
   <si>
     <t>isNotForSale</t>
   </si>
   <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>hiddenCoefficient</t>
+  </si>
+  <si>
+    <t>Red</t>
+  </si>
+  <si>
+    <t>Base Factor ( Column 'E' = 'H3' * Column 'I' )</t>
+  </si>
+  <si>
+    <t>Green</t>
+  </si>
+  <si>
+    <t>Blue</t>
+  </si>
+  <si>
+    <t>no entry item</t>
+  </si>
+  <si>
+    <t># This row is a comment.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>float</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级红宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级红宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三级红宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级绿宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级绿宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三级绿宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一级蓝宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>二级蓝宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>三级蓝宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>四级蓝宝石</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>名字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>是否缩放</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>比率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>跳过此列</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>隐藏概率</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>咖咖喱棒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>树枝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>打狗棒</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MstItemCategoryEnum</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>activate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bool</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>激活</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>expList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>经验数组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10, 20, 30,40</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>descriptList</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>描述数组</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"描述1", "描述2"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>"描述1"</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>string[]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>point</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Vector3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>点</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"x":0.0,"y":3.0,"z":2.0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>[5,7,20,40]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>["描述1", "描述4"]</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HashSet&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>createDate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>日期</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>longNum</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>long</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>sex</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>char</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>性别</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>女</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>男</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Hash</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>集合</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"a":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"a":1, "b": 2, "c": 3}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dict</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hset</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>一行空数值</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"x":1.0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"x":0.0,"y":4.0}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>表格头部的空白表示表格列的结束</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>如果第一个单元格为空，意味着表格行的结束。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DateTime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"x":1}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"x":1,"s":"ss"}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>{}</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MstItemCustomType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>customType</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>自定义类</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HideCol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>长得像日期数字</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id, key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>name,key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>注释3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>rate</t>
-  </si>
-  <si>
-    <t>category</t>
-  </si>
-  <si>
-    <t>hiddenCoefficient</t>
-  </si>
-  <si>
-    <t>Red</t>
-  </si>
-  <si>
-    <t>Base Factor ( Column 'E' = 'H3' * Column 'I' )</t>
-  </si>
-  <si>
-    <t>Green</t>
-  </si>
-  <si>
-    <t>Blue</t>
-  </si>
-  <si>
-    <t>no entry item</t>
-  </si>
-  <si>
-    <t>id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t># This row is a comment.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Dictionary&lt;string, int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>id, key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>note1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>note2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>note3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复数据X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>价格1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>price2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -103,315 +441,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>float</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级红宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级红宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三级红宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级绿宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级绿宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三级绿宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一级蓝宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>二级蓝宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>三级蓝宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>四级蓝宝石</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>名字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>价格</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>是否缩放</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>比率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>#</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>跳过此列</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>类别</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>隐藏概率</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>咖咖喱棒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>树枝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>打狗棒</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MstItemCategoryEnum</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>activate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bool</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>激活</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>时间</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>expList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>经验数组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10, 20, 30,40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>descriptList</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>描述数组</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"描述1", "描述2"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>"描述1"</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>point</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Vector3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>点</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"x":0.0,"y":3.0,"z":2.0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>[5,7,20,40]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>["描述1", "描述4"]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HashSet&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>createDate</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>longNum</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>long</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>长得像日期的数字</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>sex</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>char</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>性别</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>女</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>男</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Hash</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>集合</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"a":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"a":1, "b": 2, "c": 3}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dict</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>hset</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>一行空数值</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"x":1.0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"x":0.0,"y":4.0}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>表格头部的空白表示表格列的结束</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>如果第一个单元格为空，意味着表格行的结束。</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Dictionary&lt;string,int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DateTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DateTime</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"x":1}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"x":1,"s":"ss"}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>{}</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MstItemCustomType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>customType</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>自定义类</t>
+    <t xml:space="preserve">  类别 
+  这个是一个多行注释    </t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -573,10 +604,12 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="31" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -857,419 +890,524 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J17"/>
+  <sheetPr codeName="Sheet1"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.125" customWidth="1"/>
     <col min="2" max="2" width="12.625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="42.875" customWidth="1"/>
-    <col min="10" max="10" width="16.125" customWidth="1"/>
+    <col min="4" max="4" width="5.5" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="21.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="42.875" customWidth="1"/>
+    <col min="11" max="11" width="16.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>19</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="F1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="2"/>
+      <c r="J1" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="K1" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="H1" s="2"/>
-      <c r="I1" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:11" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="21" t="s">
-        <v>21</v>
+        <v>106</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>22</v>
+        <v>107</v>
       </c>
       <c r="C2" s="21" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="E2" s="21" t="s">
-        <v>23</v>
-      </c>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="3"/>
-      <c r="J2" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>18</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="I2" s="2"/>
+      <c r="J2" s="3"/>
+      <c r="K2" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A3" s="22"/>
       <c r="B3" s="22" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C3" s="22" t="s">
-        <v>36</v>
+        <v>104</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>37</v>
+        <v>103</v>
       </c>
       <c r="E3" s="22" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F3" s="22" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="G3" s="22" t="s">
-        <v>41</v>
-      </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="3"/>
-      <c r="J3" s="4"/>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+        <v>33</v>
+      </c>
+      <c r="H3" s="27" t="s">
+        <v>108</v>
+      </c>
+      <c r="I3" s="2"/>
+      <c r="J3" s="3"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="5">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="C4" s="5">
         <v>3</v>
       </c>
-      <c r="D4" s="6" t="b">
+      <c r="D4" s="5">
+        <f>C4*2.5</f>
+        <v>7.5</v>
+      </c>
+      <c r="E4" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="E4" s="5">
-        <f t="shared" ref="E4:E9" si="0">$I$5*J4</f>
+      <c r="F4" s="5">
+        <f t="shared" ref="F4:F9" si="0">$J$5*K4</f>
         <v>2.2999999999999998</v>
       </c>
-      <c r="F4" s="5"/>
-      <c r="G4" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I4" s="8" t="s">
-        <v>15</v>
-      </c>
-      <c r="J4" s="9">
+      <c r="G4" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J4" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="K4" s="9">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="5">
         <v>2</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C5" s="5">
         <v>10</v>
       </c>
-      <c r="D5" s="6" t="b">
+      <c r="D5" s="5">
+        <f t="shared" ref="D5:D9" si="1">C5*2.5</f>
+        <v>25</v>
+      </c>
+      <c r="E5" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="E5" s="5">
+      <c r="F5" s="5">
         <f t="shared" si="0"/>
         <v>3.2199999999999998</v>
       </c>
-      <c r="F5" s="5"/>
-      <c r="G5" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I5" s="10">
+      <c r="G5" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J5" s="10">
         <v>2.2999999999999998</v>
       </c>
-      <c r="J5" s="9">
+      <c r="K5" s="9">
         <v>1.4</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="5">
         <v>3</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="C6" s="5">
         <v>25</v>
       </c>
-      <c r="D6" s="6" t="b">
+      <c r="D6" s="5">
+        <f t="shared" si="1"/>
+        <v>62.5</v>
+      </c>
+      <c r="E6" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="E6" s="5">
+      <c r="F6" s="5">
         <f t="shared" si="0"/>
         <v>3.6799999999999997</v>
       </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="I6" s="11"/>
-      <c r="J6" s="9">
+      <c r="G6" s="5" t="s">
+        <v>95</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="J6" s="11"/>
+      <c r="K6" s="9">
         <v>1.6</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="12">
         <v>4</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C7" s="12">
         <v>60</v>
       </c>
-      <c r="D7" s="13" t="b">
+      <c r="D7" s="5">
+        <f t="shared" si="1"/>
+        <v>150</v>
+      </c>
+      <c r="E7" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E7" s="12">
+      <c r="F7" s="12">
         <f t="shared" si="0"/>
         <v>4.1399999999999997</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="11"/>
-      <c r="J7" s="9">
+      <c r="G7" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="H7" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J7" s="11"/>
+      <c r="K7" s="9">
         <v>1.8</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A8" s="12">
         <v>5</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="C8" s="12">
         <v>180</v>
       </c>
-      <c r="D8" s="13" t="b">
+      <c r="D8" s="5">
+        <f t="shared" si="1"/>
+        <v>450</v>
+      </c>
+      <c r="E8" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E8" s="12">
+      <c r="F8" s="12">
         <f t="shared" si="0"/>
         <v>4.83</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="11"/>
-      <c r="J8" s="9">
+      <c r="G8" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J8" s="11"/>
+      <c r="K8" s="9">
         <v>2.1</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A9" s="12">
         <v>6</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="C9" s="12">
         <v>230</v>
       </c>
-      <c r="D9" s="13" t="b">
+      <c r="D9" s="5">
+        <f t="shared" si="1"/>
+        <v>575</v>
+      </c>
+      <c r="E9" s="13" t="b">
         <v>1</v>
       </c>
-      <c r="E9" s="12">
+      <c r="F9" s="12">
         <f t="shared" si="0"/>
         <v>5.0599999999999996</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="H9" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="J9" s="11"/>
+      <c r="K9" s="9">
+        <v>2.2000000000000002</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A10" s="15" t="s">
         <v>16</v>
-      </c>
-      <c r="I9" s="11"/>
-      <c r="J9" s="9">
-        <v>2.2000000000000002</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" s="15" t="s">
-        <v>20</v>
       </c>
       <c r="B10" s="15"/>
       <c r="C10" s="15"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="15"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="16"/>
       <c r="F10" s="15"/>
-      <c r="G10" s="16"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="G10" s="15"/>
+      <c r="H10" s="16"/>
+      <c r="J10" s="11"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="17">
         <v>7</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C11" s="17">
         <v>310</v>
       </c>
-      <c r="D11" s="18" t="b">
+      <c r="D11" s="17">
+        <f>C11*0.78</f>
+        <v>241.8</v>
+      </c>
+      <c r="E11" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="E11" s="17">
-        <f>$I$5*J11</f>
+      <c r="F11" s="17">
+        <f>$J$5*K11</f>
         <v>5.52</v>
       </c>
-      <c r="F11" s="17"/>
-      <c r="G11" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="11"/>
-      <c r="J11" s="9">
+      <c r="G11" s="17">
+        <v>0</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J11" s="11"/>
+      <c r="K11" s="9">
         <v>2.4</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A12" s="17">
         <v>8</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C12" s="17">
         <v>560</v>
       </c>
-      <c r="D12" s="18" t="b">
+      <c r="D12" s="17">
+        <f t="shared" ref="D12:D15" si="2">C12*0.78</f>
+        <v>436.8</v>
+      </c>
+      <c r="E12" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="E12" s="17">
-        <f>$I$5*J12</f>
+      <c r="F12" s="17">
+        <f>$J$5*K12</f>
         <v>5.9799999999999995</v>
       </c>
-      <c r="F12" s="17"/>
-      <c r="G12" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I12" s="11"/>
-      <c r="J12" s="9">
+      <c r="G12" s="17">
+        <v>0</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J12" s="11"/>
+      <c r="K12" s="9">
         <v>2.6</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="17">
         <v>9</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="C13" s="17">
         <v>820</v>
       </c>
-      <c r="D13" s="18" t="b">
+      <c r="D13" s="17">
+        <f t="shared" si="2"/>
+        <v>639.6</v>
+      </c>
+      <c r="E13" s="18" t="b">
         <v>0</v>
       </c>
-      <c r="E13" s="17">
-        <f>$I$5*J13</f>
+      <c r="F13" s="17">
+        <f>$J$5*K13</f>
         <v>6.4399999999999995</v>
       </c>
-      <c r="F13" s="17"/>
-      <c r="G13" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="11"/>
-      <c r="J13" s="9">
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J13" s="11"/>
+      <c r="K13" s="9">
         <v>2.8</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A14" s="17">
         <v>10</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C14" s="17">
         <v>1010</v>
       </c>
-      <c r="D14" s="18" t="b">
+      <c r="D14" s="17">
+        <f t="shared" si="2"/>
+        <v>787.80000000000007</v>
+      </c>
+      <c r="E14" s="18" t="b">
         <v>1</v>
       </c>
-      <c r="E14" s="17">
-        <f>$I$5*J14</f>
+      <c r="F14" s="17">
+        <f>$J$5*K14</f>
         <v>8.0499999999999989</v>
       </c>
-      <c r="F14" s="17"/>
-      <c r="G14" s="19" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="11"/>
-      <c r="J14" s="9">
+      <c r="G14" s="17">
+        <v>0</v>
+      </c>
+      <c r="H14" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J14" s="11"/>
+      <c r="K14" s="9">
         <v>3.5</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" t="s">
-        <v>92</v>
-      </c>
-      <c r="I16" s="11"/>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A17" s="15">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="17">
+        <v>10</v>
+      </c>
+      <c r="B15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="C15" s="17">
+        <v>1010</v>
+      </c>
+      <c r="D15" s="17">
+        <f t="shared" si="2"/>
+        <v>787.80000000000007</v>
+      </c>
+      <c r="E15" s="18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F15" s="17">
+        <f>$J$5*K15</f>
+        <v>8.0499999999999989</v>
+      </c>
+      <c r="G15" s="17" t="s">
+        <v>102</v>
+      </c>
+      <c r="H15" s="19" t="s">
+        <v>14</v>
+      </c>
+      <c r="J15" s="11"/>
+      <c r="K15" s="9">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A18" s="15">
         <v>99</v>
       </c>
-      <c r="B17" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="15">
+      <c r="B18" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C18" s="15">
         <v>0</v>
       </c>
-      <c r="D17" s="20" t="b">
+      <c r="D18" s="15"/>
+      <c r="E18" s="20" t="b">
         <v>0</v>
       </c>
-      <c r="E17" s="15">
-        <f>$I$5*J17</f>
+      <c r="F18" s="15">
+        <f>$J$5*K18</f>
         <v>22.77</v>
       </c>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="I17" s="11"/>
-      <c r="J17" s="9">
+      <c r="G18" s="15"/>
+      <c r="H18" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J18" s="11"/>
+      <c r="K18" s="9">
         <v>9.9</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="D4:D9 D11:D14">
+    <dataValidation type="list" operator="equal" showErrorMessage="1" sqref="E4:E9 E11:E15">
       <formula1>"FALSE,TRUE"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G14">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H4:H15">
       <formula1>"Red,Green,Blue"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -1281,157 +1419,155 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O7"/>
+  <sheetPr codeName="Sheet2"/>
+  <dimension ref="A1:P7"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="6" max="6" width="15.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.375" customWidth="1"/>
-    <col min="8" max="8" width="17.25" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.375" customWidth="1"/>
-    <col min="11" max="11" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.125" customWidth="1"/>
+    <col min="3" max="3" width="5.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.375" customWidth="1"/>
+    <col min="7" max="7" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.375" customWidth="1"/>
+    <col min="10" max="10" width="18.75" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" t="s">
+        <v>63</v>
+      </c>
+      <c r="H1" t="s">
+        <v>45</v>
+      </c>
+      <c r="I1" t="s">
+        <v>49</v>
+      </c>
+      <c r="J1" t="s">
+        <v>54</v>
+      </c>
+      <c r="K1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" t="s">
+        <v>75</v>
+      </c>
+      <c r="M1" t="s">
+        <v>87</v>
+      </c>
+      <c r="P1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" t="s">
+        <v>66</v>
+      </c>
+      <c r="D2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H2" t="s">
+        <v>46</v>
+      </c>
+      <c r="I2" t="s">
+        <v>53</v>
+      </c>
+      <c r="J2" t="s">
+        <v>55</v>
+      </c>
+      <c r="K2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L2" t="s">
+        <v>97</v>
+      </c>
+      <c r="M2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="B3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>76</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D3" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" t="s">
+        <v>62</v>
+      </c>
+      <c r="G3" t="s">
+        <v>90</v>
+      </c>
+      <c r="H3" t="s">
+        <v>47</v>
+      </c>
+      <c r="I3" t="s">
         <v>50</v>
       </c>
-      <c r="F1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="J3" t="s">
+        <v>56</v>
+      </c>
+      <c r="K3" t="s">
         <v>71</v>
       </c>
-      <c r="H1" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J1" t="s">
-        <v>59</v>
-      </c>
-      <c r="K1" t="s">
-        <v>64</v>
-      </c>
-      <c r="L1" t="s">
-        <v>87</v>
-      </c>
-      <c r="M1" t="s">
-        <v>86</v>
-      </c>
-      <c r="N1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>77</v>
-      </c>
-      <c r="D2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" t="s">
-        <v>94</v>
-      </c>
-      <c r="G2" t="s">
-        <v>95</v>
-      </c>
-      <c r="H2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I2" t="s">
-        <v>56</v>
-      </c>
-      <c r="J2" t="s">
-        <v>63</v>
-      </c>
-      <c r="K2" t="s">
-        <v>65</v>
-      </c>
-      <c r="L2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" t="s">
-        <v>93</v>
-      </c>
-      <c r="N2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D3" t="s">
-        <v>4</v>
-      </c>
-      <c r="E3" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="L3" t="s">
         <v>72</v>
       </c>
-      <c r="H3" t="s">
-        <v>75</v>
-      </c>
-      <c r="I3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J3" t="s">
-        <v>60</v>
-      </c>
-      <c r="K3" t="s">
-        <v>66</v>
-      </c>
-      <c r="L3" t="s">
-        <v>82</v>
-      </c>
       <c r="M3" t="s">
-        <v>83</v>
-      </c>
-      <c r="N3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.2">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A4" s="23" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -1440,42 +1576,39 @@
         <v>1</v>
       </c>
       <c r="F4" s="24">
-        <v>45911.871354166666</v>
+        <v>45912</v>
       </c>
       <c r="G4" s="25">
-        <v>45912</v>
-      </c>
-      <c r="H4" s="26">
         <v>123</v>
       </c>
+      <c r="H4" t="s">
+        <v>48</v>
+      </c>
       <c r="I4" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
+        <v>48</v>
       </c>
       <c r="L4" t="s">
-        <v>58</v>
+        <v>73</v>
       </c>
       <c r="M4" t="s">
-        <v>84</v>
-      </c>
-      <c r="N4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="23" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C5" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="D5">
         <v>1.3</v>
@@ -1484,42 +1617,39 @@
         <v>0</v>
       </c>
       <c r="F5" s="24">
-        <v>45912.871354108793</v>
+        <v>45913</v>
       </c>
       <c r="G5" s="25">
-        <v>45913</v>
-      </c>
-      <c r="H5" s="26">
         <v>2017001</v>
       </c>
+      <c r="H5" t="s">
+        <v>58</v>
+      </c>
       <c r="I5" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="J5" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="K5" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="L5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M5" t="s">
-        <v>85</v>
-      </c>
-      <c r="N5" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.2">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A6" s="23" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="B6" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="D6">
         <v>99.99</v>
@@ -1528,42 +1658,38 @@
         <v>1</v>
       </c>
       <c r="F6" s="24">
-        <v>45913.871354108793</v>
-      </c>
-      <c r="G6" s="25">
         <v>45914</v>
       </c>
-      <c r="H6" s="23">
+      <c r="G6" s="23">
         <v>20151224</v>
       </c>
-      <c r="I6">
+      <c r="H6">
         <v>99</v>
       </c>
+      <c r="I6" t="s">
+        <v>59</v>
+      </c>
       <c r="J6" t="s">
-        <v>69</v>
-      </c>
-      <c r="K6" t="s">
-        <v>89</v>
-      </c>
-      <c r="L6">
+        <v>78</v>
+      </c>
+      <c r="K6">
         <v>99</v>
+      </c>
+      <c r="L6" t="s">
+        <v>74</v>
       </c>
       <c r="M6" t="s">
         <v>85</v>
       </c>
-      <c r="N6" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A7" s="27">
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A7" s="26">
         <v>4</v>
       </c>
       <c r="F7" s="24"/>
-      <c r="G7" s="25"/>
-      <c r="H7" s="23"/>
-      <c r="O7" t="s">
-        <v>88</v>
+      <c r="G7" s="23"/>
+      <c r="N7" t="s">
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/UnityExcelImporterX/Example/Excels/MsItems.xlsx
+++ b/Assets/UnityExcelImporterX/Example/Excels/MsItems.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="110">
   <si>
     <t>name</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -443,6 +443,10 @@
   <si>
     <t xml:space="preserve">  类别 
   这个是一个多行注释    </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>#10</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1333,8 +1337,8 @@
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A15" s="17">
-        <v>10</v>
+      <c r="A15" s="17" t="s">
+        <v>109</v>
       </c>
       <c r="B15" s="17" t="s">
         <v>28</v>
